--- a/addresses/mock_google_data/distance_matrices/05_distance_matrix_group-0.xlsx
+++ b/addresses/mock_google_data/distance_matrices/05_distance_matrix_group-0.xlsx
@@ -513,7 +513,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -528,13 +528,13 @@
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
@@ -568,55 +568,55 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
         <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N3" t="n">
+        <v>11</v>
+      </c>
+      <c r="O3" t="n">
         <v>12</v>
       </c>
-      <c r="O3" t="n">
-        <v>14</v>
-      </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -629,13 +629,13 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -684,55 +684,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
         <v>12</v>
       </c>
-      <c r="G5" t="n">
-        <v>11</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="N5" t="n">
         <v>12</v>
       </c>
-      <c r="I5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>13</v>
-      </c>
-      <c r="N5" t="n">
-        <v>13</v>
-      </c>
       <c r="O5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -745,7 +745,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -760,19 +760,19 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -812,13 +812,13 @@
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -827,7 +827,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>11</v>
@@ -836,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
@@ -845,10 +845,10 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -861,13 +861,13 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
         <v>4</v>
@@ -900,7 +900,7 @@
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
@@ -919,14 +919,14 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
         <v>9</v>
       </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>11</v>
-      </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
@@ -946,7 +946,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
         <v>4</v>
@@ -977,13 +977,13 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -992,10 +992,10 @@
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1004,13 +1004,13 @@
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
         <v>2</v>
@@ -1035,7 +1035,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -1090,55 +1090,55 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13</v>
+      </c>
+      <c r="N12" t="n">
+        <v>13</v>
+      </c>
+      <c r="O12" t="n">
         <v>12</v>
       </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="P12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q12" t="n">
         <v>13</v>
       </c>
-      <c r="G12" t="n">
+      <c r="R12" t="n">
         <v>12</v>
-      </c>
-      <c r="H12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>14</v>
-      </c>
-      <c r="N12" t="n">
-        <v>14</v>
-      </c>
-      <c r="O12" t="n">
-        <v>14</v>
-      </c>
-      <c r="P12" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>14</v>
-      </c>
-      <c r="R12" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1151,13 +1151,13 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1209,13 +1209,13 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -1224,7 +1224,7 @@
         <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
@@ -1236,7 +1236,7 @@
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
@@ -1267,7 +1267,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
@@ -1291,7 +1291,7 @@
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>12</v>
@@ -1300,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -1334,13 +1334,13 @@
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -1349,7 +1349,7 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>11</v>
@@ -1358,7 +1358,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1367,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1383,13 +1383,13 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1410,7 +1410,7 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
         <v>4</v>
@@ -1441,34 +1441,34 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
         <v>12</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>13</v>
       </c>
       <c r="M18" t="n">
         <v>5</v>
